--- a/Day2.xlsx
+++ b/Day2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/utkarsh/Downloads/Accio_excel/Excel-for-DA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96723AE6-659D-0A42-93B6-81C54EFF4E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8006B35F-85E3-564C-861B-010F7BC016B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" activeTab="1" xr2:uid="{DC7F8EAD-DEA2-3349-B59D-804B69E5A80F}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="agenda" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -385,13 +385,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -471,13 +470,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -487,6 +479,13 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -564,8 +563,8 @@
       <xdr:row>108</xdr:row>
       <xdr:rowOff>186399</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="3" name="Ink 2">
@@ -584,7 +583,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="3" name="Ink 2">
@@ -629,8 +628,8 @@
       <xdr:row>106</xdr:row>
       <xdr:rowOff>181920</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="5" name="Ink 4">
@@ -649,7 +648,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="5" name="Ink 4">
@@ -694,8 +693,8 @@
       <xdr:row>108</xdr:row>
       <xdr:rowOff>80559</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="6" name="Ink 5">
@@ -714,7 +713,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="6" name="Ink 5">
@@ -834,7 +833,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{91C0464A-355F-D64B-8103-9C4BDBB4A0CD}" name="Table1" displayName="Table1" ref="B24:D54" totalsRowShown="0" headerRowBorderDxfId="4" tableBorderDxfId="5" totalsRowBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{91C0464A-355F-D64B-8103-9C4BDBB4A0CD}" name="Table1" displayName="Table1" ref="B24:D54" totalsRowShown="0" headerRowBorderDxfId="5" tableBorderDxfId="4" totalsRowBorderDxfId="3">
   <autoFilter ref="B24:D54" xr:uid="{91C0464A-355F-D64B-8103-9C4BDBB4A0CD}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B25:D54">
     <sortCondition descending="1" ref="C24:C54"/>
@@ -1348,86 +1347,86 @@
       <c r="H51" s="1"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C55" s="9"/>
-      <c r="D55" s="10"/>
-      <c r="E55" s="10" t="s">
+      <c r="C55" s="8"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F55" s="10"/>
-      <c r="G55" s="10"/>
-      <c r="H55" s="10"/>
-      <c r="I55" s="10"/>
-      <c r="J55" s="10"/>
-      <c r="K55" s="10" t="s">
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9"/>
+      <c r="K55" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="9"/>
-      <c r="D56" s="10"/>
-      <c r="E56" s="10" t="s">
+      <c r="C56" s="8"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F56" s="10"/>
-      <c r="G56" s="10"/>
-      <c r="H56" s="10"/>
-      <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
-      <c r="K56" s="10" t="s">
+      <c r="F56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9"/>
+      <c r="K56" s="9" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="10"/>
-      <c r="E57" s="10"/>
-      <c r="F57" s="10"/>
-      <c r="G57" s="10"/>
-      <c r="H57" s="10"/>
-      <c r="I57" s="10"/>
-      <c r="J57" s="10"/>
-      <c r="K57" s="10"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
+      <c r="K57" s="9"/>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C58" s="9"/>
-      <c r="D58" s="10"/>
-      <c r="E58" s="10" t="s">
+      <c r="C58" s="8"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F58" s="10"/>
-      <c r="G58" s="10"/>
-      <c r="H58" s="10"/>
-      <c r="I58" s="10"/>
-      <c r="J58" s="10"/>
-      <c r="K58" s="10" t="s">
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
+      <c r="K58" s="9" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C59" s="9"/>
-      <c r="D59" s="10"/>
-      <c r="E59" s="10" t="s">
+      <c r="C59" s="8"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F59" s="10"/>
-      <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
-      <c r="I59" s="10"/>
-      <c r="J59" s="10"/>
-      <c r="K59" s="10" t="s">
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="9"/>
+      <c r="J59" s="9"/>
+      <c r="K59" s="9" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1756,13 +1755,13 @@
       <c r="D3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H3" s="3"/>
@@ -1777,7 +1776,7 @@
       <c r="D4" s="4">
         <v>0.1</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <f>B4*C4*(1-D4)</f>
         <v>360</v>
       </c>
@@ -1789,7 +1788,10 @@
         <f>E4*$E$1</f>
         <v>64.8</v>
       </c>
-      <c r="H4" s="3"/>
+      <c r="H4" s="3" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(G4)</f>
+        <v>=E4*$E$1</v>
+      </c>
     </row>
     <row r="5" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B5" s="3">
@@ -1801,7 +1803,7 @@
       <c r="D5" s="4">
         <v>0.05</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <f t="shared" ref="E5:E8" si="0">B5*C5*(1-D5)</f>
         <v>1425</v>
       </c>
@@ -1813,7 +1815,10 @@
         <f t="shared" ref="G5:G8" si="2">E5*$E$1</f>
         <v>256.5</v>
       </c>
-      <c r="H5" s="3"/>
+      <c r="H5" s="3" t="str">
+        <f t="shared" ref="H5:H8" ca="1" si="3">_xlfn.FORMULATEXT(G5)</f>
+        <v>=E5*$E$1</v>
+      </c>
     </row>
     <row r="6" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B6" s="3">
@@ -1825,19 +1830,22 @@
       <c r="D6" s="4">
         <v>0</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
       <c r="F6" s="3" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">_xlfn.FORMULATEXT(E6)</f>
         <v>=B6*C6*(1-D6)</v>
       </c>
       <c r="G6" s="3">
         <f t="shared" si="2"/>
         <v>28.799999999999997</v>
       </c>
-      <c r="H6" s="3"/>
+      <c r="H6" s="3" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>=E6*$E$1</v>
+      </c>
     </row>
     <row r="7" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B7" s="3">
@@ -1849,7 +1857,7 @@
       <c r="D7" s="4">
         <v>0</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <f t="shared" si="0"/>
         <v>4400</v>
       </c>
@@ -1861,7 +1869,10 @@
         <f t="shared" si="2"/>
         <v>792</v>
       </c>
-      <c r="H7" s="3"/>
+      <c r="H7" s="3" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>=E7*$E$1</v>
+      </c>
     </row>
     <row r="8" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B8" s="3">
@@ -1873,7 +1884,7 @@
       <c r="D8" s="4">
         <v>0.2</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
@@ -1885,7 +1896,10 @@
         <f t="shared" si="2"/>
         <v>8.64</v>
       </c>
-      <c r="H8" s="3"/>
+      <c r="H8" s="3" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>=E8*$E$1</v>
+      </c>
     </row>
     <row r="10" spans="2:23" x14ac:dyDescent="0.2">
       <c r="G10" s="2"/>
@@ -1897,7 +1911,7 @@
         <f ca="1">_xlfn.FORMULATEXT(B12)</f>
         <v>=B3:G8</v>
       </c>
-      <c r="F11" s="7"/>
+      <c r="F11" s="6"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -2075,12 +2089,12 @@
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="8"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="7"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="E22" s="2"/>
@@ -2089,346 +2103,346 @@
       <c r="E23" s="2"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="15" t="s">
         <v>12</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B25" s="12">
+      <c r="B25" s="11">
         <v>10</v>
       </c>
       <c r="C25" s="3">
         <v>440</v>
       </c>
-      <c r="D25" s="13">
+      <c r="D25" s="12">
         <v>0</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B26" s="12">
+      <c r="B26" s="11">
         <v>10</v>
       </c>
       <c r="C26" s="3">
         <v>440</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D26" s="12">
         <v>0</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B27" s="12">
+      <c r="B27" s="11">
         <v>10</v>
       </c>
       <c r="C27" s="3">
         <v>440</v>
       </c>
-      <c r="D27" s="13">
+      <c r="D27" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B28" s="12">
+      <c r="B28" s="11">
         <v>10</v>
       </c>
       <c r="C28" s="3">
         <v>440</v>
       </c>
-      <c r="D28" s="13">
+      <c r="D28" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B29" s="12">
+      <c r="B29" s="11">
         <v>10</v>
       </c>
       <c r="C29" s="3">
         <v>440</v>
       </c>
-      <c r="D29" s="13">
+      <c r="D29" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B30" s="12">
+      <c r="B30" s="11">
         <v>10</v>
       </c>
       <c r="C30" s="3">
         <v>440</v>
       </c>
-      <c r="D30" s="13">
+      <c r="D30" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B31" s="12">
+      <c r="B31" s="11">
         <v>5</v>
       </c>
       <c r="C31" s="3">
         <v>300</v>
       </c>
-      <c r="D31" s="13">
+      <c r="D31" s="12">
         <v>0.05</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B32" s="12">
+      <c r="B32" s="11">
         <v>5</v>
       </c>
       <c r="C32" s="3">
         <v>300</v>
       </c>
-      <c r="D32" s="13">
+      <c r="D32" s="12">
         <v>0.05</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B33" s="12">
+      <c r="B33" s="11">
         <v>5</v>
       </c>
       <c r="C33" s="3">
         <v>300</v>
       </c>
-      <c r="D33" s="13">
+      <c r="D33" s="12">
         <v>0.05</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B34" s="12">
+      <c r="B34" s="11">
         <v>5</v>
       </c>
       <c r="C34" s="3">
         <v>300</v>
       </c>
-      <c r="D34" s="13">
+      <c r="D34" s="12">
         <v>0.05</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B35" s="12">
+      <c r="B35" s="11">
         <v>5</v>
       </c>
       <c r="C35" s="3">
         <v>300</v>
       </c>
-      <c r="D35" s="13">
+      <c r="D35" s="12">
         <v>0.05</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B36" s="12">
+      <c r="B36" s="11">
         <v>5</v>
       </c>
       <c r="C36" s="3">
         <v>300</v>
       </c>
-      <c r="D36" s="13">
+      <c r="D36" s="12">
         <v>0.05</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B37" s="12">
+      <c r="B37" s="11">
         <v>4</v>
       </c>
       <c r="C37" s="3">
         <v>100</v>
       </c>
-      <c r="D37" s="13">
+      <c r="D37" s="12">
         <v>0.1</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B38" s="12">
+      <c r="B38" s="11">
         <v>4</v>
       </c>
       <c r="C38" s="3">
         <v>100</v>
       </c>
-      <c r="D38" s="13">
+      <c r="D38" s="12">
         <v>0.1</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B39" s="12">
+      <c r="B39" s="11">
         <v>4</v>
       </c>
       <c r="C39" s="3">
         <v>100</v>
       </c>
-      <c r="D39" s="13">
+      <c r="D39" s="12">
         <v>0.1</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B40" s="12">
+      <c r="B40" s="11">
         <v>4</v>
       </c>
       <c r="C40" s="3">
         <v>100</v>
       </c>
-      <c r="D40" s="13">
+      <c r="D40" s="12">
         <v>0.1</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B41" s="12">
+      <c r="B41" s="11">
         <v>4</v>
       </c>
       <c r="C41" s="3">
         <v>100</v>
       </c>
-      <c r="D41" s="13">
+      <c r="D41" s="12">
         <v>0.1</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B42" s="12">
+      <c r="B42" s="11">
         <v>4</v>
       </c>
       <c r="C42" s="3">
         <v>100</v>
       </c>
-      <c r="D42" s="13">
+      <c r="D42" s="12">
         <v>0.1</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B43" s="12">
+      <c r="B43" s="11">
         <v>2</v>
       </c>
       <c r="C43" s="3">
         <v>30</v>
       </c>
-      <c r="D43" s="13">
+      <c r="D43" s="12">
         <v>0.2</v>
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B44" s="12">
+      <c r="B44" s="11">
         <v>2</v>
       </c>
       <c r="C44" s="3">
         <v>30</v>
       </c>
-      <c r="D44" s="13">
+      <c r="D44" s="12">
         <v>0.2</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B45" s="12">
+      <c r="B45" s="11">
         <v>2</v>
       </c>
       <c r="C45" s="3">
         <v>30</v>
       </c>
-      <c r="D45" s="13">
+      <c r="D45" s="12">
         <v>0.2</v>
       </c>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B46" s="12">
+      <c r="B46" s="11">
         <v>2</v>
       </c>
       <c r="C46" s="3">
         <v>30</v>
       </c>
-      <c r="D46" s="13">
+      <c r="D46" s="12">
         <v>0.2</v>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B47" s="12">
+      <c r="B47" s="11">
         <v>2</v>
       </c>
       <c r="C47" s="3">
         <v>30</v>
       </c>
-      <c r="D47" s="13">
+      <c r="D47" s="12">
         <v>0.2</v>
       </c>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B48" s="12">
+      <c r="B48" s="11">
         <v>2</v>
       </c>
       <c r="C48" s="3">
         <v>30</v>
       </c>
-      <c r="D48" s="13">
+      <c r="D48" s="12">
         <v>0.2</v>
       </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B49" s="12">
+      <c r="B49" s="11">
         <v>8</v>
       </c>
       <c r="C49" s="3">
         <v>20</v>
       </c>
-      <c r="D49" s="13">
+      <c r="D49" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B50" s="12">
+      <c r="B50" s="11">
         <v>8</v>
       </c>
       <c r="C50" s="3">
         <v>20</v>
       </c>
-      <c r="D50" s="13">
+      <c r="D50" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B51" s="12">
+      <c r="B51" s="11">
         <v>8</v>
       </c>
       <c r="C51" s="3">
         <v>20</v>
       </c>
-      <c r="D51" s="13">
+      <c r="D51" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B52" s="12">
+      <c r="B52" s="11">
         <v>8</v>
       </c>
       <c r="C52" s="3">
         <v>20</v>
       </c>
-      <c r="D52" s="13">
+      <c r="D52" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B53" s="12">
+      <c r="B53" s="11">
         <v>8</v>
       </c>
       <c r="C53" s="3">
         <v>20</v>
       </c>
-      <c r="D53" s="13">
+      <c r="D53" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B54" s="17">
+      <c r="B54" s="16">
         <v>8</v>
       </c>
-      <c r="C54" s="18">
+      <c r="C54" s="17">
         <v>20</v>
       </c>
-      <c r="D54" s="19">
+      <c r="D54" s="18">
         <v>0</v>
       </c>
     </row>
